--- a/data/ams_weekly_data/Audio_Array/business_report_week33.xlsx
+++ b/data/ams_weekly_data/Audio_Array/business_report_week33.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="478">
   <si>
     <t>SKU</t>
   </si>
@@ -166,6 +166,9 @@
     <t>FBA76597</t>
   </si>
   <si>
+    <t>FBA78206</t>
+  </si>
+  <si>
     <t>FBA78203</t>
   </si>
   <si>
@@ -628,6 +631,9 @@
     <t>AA-06</t>
   </si>
   <si>
+    <t>AM-W15</t>
+  </si>
+  <si>
     <t>AM-C30</t>
   </si>
   <si>
@@ -1058,6 +1064,9 @@
   </si>
   <si>
     <t>B0BQ7H7418</t>
+  </si>
+  <si>
+    <t>B0C4YSV3XL</t>
   </si>
   <si>
     <t>B0C4YTNJG7</t>
@@ -1796,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W155"/>
+  <dimension ref="A1:W156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1875,16 +1884,16 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F2">
         <v>13912</v>
@@ -1917,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1929,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>422277.74</v>
+        <v>492165.14</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1946,16 +1955,16 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F3">
         <v>138</v>
@@ -2017,16 +2026,16 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F4">
         <v>441</v>
@@ -2059,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -2071,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>42529.92</v>
+        <v>48619.75999999999</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -2088,16 +2097,16 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F5">
         <v>292</v>
@@ -2159,16 +2168,16 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F6">
         <v>911</v>
@@ -2201,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2213,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>22530.5</v>
+        <v>24139.82</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -2230,16 +2239,16 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F7">
         <v>1706</v>
@@ -2301,13 +2310,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2369,16 +2378,16 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F9">
         <v>718</v>
@@ -2440,16 +2449,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F10">
         <v>255</v>
@@ -2482,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2494,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>17569.5</v>
+        <v>22955.96</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -2511,16 +2520,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F11">
         <v>129</v>
@@ -2553,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2565,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>6918.64</v>
+        <v>13837.28</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -2582,16 +2591,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F12">
         <v>251</v>
@@ -2624,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2636,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>11401.27</v>
+        <v>14448.71</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -2653,16 +2662,16 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F13">
         <v>562</v>
@@ -2695,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2707,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>5327.12</v>
+        <v>6468.65</v>
       </c>
       <c r="U13">
         <v>0</v>
@@ -2724,16 +2733,16 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F14">
         <v>431</v>
@@ -2766,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2778,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>14112.73</v>
+        <v>16120.36</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -2795,16 +2804,16 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F15">
         <v>1898</v>
@@ -2866,16 +2875,16 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F16">
         <v>1128</v>
@@ -2937,16 +2946,16 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F17">
         <v>660</v>
@@ -2979,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -2991,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>18153.36</v>
+        <v>20479.63</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -3008,13 +3017,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3076,13 +3085,13 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3144,16 +3153,16 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -3215,13 +3224,13 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3283,16 +3292,16 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -3354,16 +3363,16 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F23">
         <v>9</v>
@@ -3425,16 +3434,16 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F24">
         <v>1331</v>
@@ -3467,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -3479,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>42479.97</v>
+        <v>45102.01</v>
       </c>
       <c r="U24">
         <v>0</v>
@@ -3496,16 +3505,16 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D25" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F25">
         <v>9484</v>
@@ -3538,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3550,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>554465.9399999999</v>
+        <v>657409.1699999999</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3567,16 +3576,16 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D26" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F26">
         <v>1376</v>
@@ -3638,16 +3647,16 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D27" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F27">
         <v>152</v>
@@ -3709,16 +3718,16 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F28">
         <v>294</v>
@@ -3751,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -3763,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>14328.8</v>
+        <v>16361</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3780,19 +3789,16 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D29" t="s">
-        <v>348</v>
-      </c>
-      <c r="E29" t="s">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="F29">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3804,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3851,19 +3857,19 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3875,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -3922,19 +3928,19 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3946,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -3993,19 +3999,19 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D32" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F32">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4017,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>239</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -4035,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4047,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>5828.82</v>
+        <v>0</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -4064,19 +4070,19 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D33" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F33">
-        <v>826</v>
+        <v>167</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4088,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>1140</v>
+        <v>239</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -4106,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4118,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>15282.21</v>
+        <v>5828.82</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -4135,19 +4141,19 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F34">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4159,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>1261</v>
+        <v>1140</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -4177,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -4189,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>80367.72</v>
+        <v>16552.55</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -4206,19 +4212,19 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C35" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D35" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F35">
-        <v>155</v>
+        <v>836</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4230,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>226</v>
+        <v>1261</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -4248,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -4260,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>95812.62</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -4277,16 +4283,19 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D36" t="s">
-        <v>355</v>
+        <v>357</v>
+      </c>
+      <c r="E36" t="s">
+        <v>212</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4298,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -4316,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -4328,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>17791.51</v>
+        <v>0</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -4345,19 +4354,16 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D37" t="s">
-        <v>356</v>
-      </c>
-      <c r="E37" t="s">
-        <v>212</v>
+        <v>358</v>
       </c>
       <c r="F37">
-        <v>1645</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4369,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>2248</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -4387,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -4399,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>71131.85000000001</v>
+        <v>17791.51</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -4416,16 +4422,19 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D38" t="s">
-        <v>357</v>
+        <v>359</v>
+      </c>
+      <c r="E38" t="s">
+        <v>214</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1645</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4437,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -4455,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -4467,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>2567.8</v>
+        <v>80027.61</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -4484,19 +4493,16 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D39" t="s">
-        <v>358</v>
-      </c>
-      <c r="E39" t="s">
-        <v>214</v>
+        <v>360</v>
       </c>
       <c r="F39">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -4538,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>1269.5</v>
+        <v>2567.8</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -4555,19 +4561,19 @@
         <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C40" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D40" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F40">
-        <v>936</v>
+        <v>194</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4579,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>1474</v>
+        <v>260</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4597,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -4609,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>34057.57</v>
+        <v>1904.24</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -4626,19 +4632,19 @@
         <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F41">
-        <v>997</v>
+        <v>936</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4650,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>1206</v>
+        <v>1474</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -4668,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -4680,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>4561.01</v>
+        <v>38064.34</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -4697,19 +4703,19 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C42" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D42" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F42">
-        <v>122</v>
+        <v>997</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4721,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>176</v>
+        <v>1206</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -4739,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -4751,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4561.01</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -4768,19 +4774,19 @@
         <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C43" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D43" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F43">
-        <v>934</v>
+        <v>122</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4792,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>1472</v>
+        <v>176</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4810,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -4822,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>25975.65</v>
+        <v>0</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -4839,19 +4845,19 @@
         <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D44" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F44">
-        <v>559</v>
+        <v>934</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4863,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>765</v>
+        <v>1472</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -4881,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -4893,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>3404.24</v>
+        <v>33452.81</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -4910,19 +4916,19 @@
         <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D45" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F45">
-        <v>3324</v>
+        <v>559</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4934,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>4737</v>
+        <v>765</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -4952,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -4964,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="T45">
-        <v>414574.85</v>
+        <v>4081.36</v>
       </c>
       <c r="U45">
         <v>0</v>
@@ -4981,19 +4987,19 @@
         <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D46" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F46">
-        <v>1341</v>
+        <v>3324</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5005,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1976</v>
+        <v>4737</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -5023,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -5035,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="T46">
-        <v>33348.29</v>
+        <v>464801.98</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -5052,19 +5058,19 @@
         <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D47" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F47">
-        <v>1641</v>
+        <v>1341</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5076,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>2443</v>
+        <v>1976</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -5094,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -5106,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>40384.73</v>
+        <v>35720.32</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -5123,19 +5129,19 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D48" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F48">
-        <v>2264</v>
+        <v>1641</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5147,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>3037</v>
+        <v>2443</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -5165,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -5177,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="T48">
-        <v>24600.39</v>
+        <v>46685.56</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -5194,19 +5200,19 @@
         <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D49" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F49">
-        <v>265</v>
+        <v>2264</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5218,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>345</v>
+        <v>3037</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -5236,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -5248,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="T49">
-        <v>2860.15</v>
+        <v>27826.65</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -5265,19 +5271,19 @@
         <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F50">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5289,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -5307,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -5319,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>20395.76</v>
+        <v>5720.31</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -5336,19 +5342,19 @@
         <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D51" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F51">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5360,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -5378,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -5390,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>931.36</v>
+        <v>20395.76</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -5407,19 +5413,19 @@
         <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F52">
-        <v>124</v>
+        <v>226</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5431,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>167</v>
+        <v>277</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -5449,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -5461,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>931.36</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -5478,19 +5484,19 @@
         <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C53" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D53" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F53">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5502,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -5549,19 +5555,19 @@
         <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D54" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F54">
-        <v>255</v>
+        <v>137</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5573,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>355</v>
+        <v>157</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -5591,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -5603,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="T54">
-        <v>5523.72</v>
+        <v>0</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -5620,19 +5626,19 @@
         <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F55">
-        <v>3404</v>
+        <v>255</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5644,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>4296</v>
+        <v>355</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -5662,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -5674,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>41063.55</v>
+        <v>5523.72</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -5691,19 +5697,19 @@
         <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C56" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D56" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F56">
-        <v>429</v>
+        <v>3404</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5715,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>509</v>
+        <v>4296</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -5733,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -5745,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="T56">
-        <v>19138.99</v>
+        <v>46536.43</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -5762,19 +5768,19 @@
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C57" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D57" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F57">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5786,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>465</v>
+        <v>509</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -5804,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -5816,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="T57">
-        <v>11183.9</v>
+        <v>19138.99</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -5833,19 +5839,19 @@
         <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C58" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D58" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F58">
-        <v>230</v>
+        <v>404</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -5857,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -5875,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -5887,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="T58">
-        <v>2878.82</v>
+        <v>11183.9</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -5904,19 +5910,19 @@
         <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C59" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D59" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F59">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -5928,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>692</v>
+        <v>295</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -5946,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -5958,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>12200</v>
+        <v>2878.82</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -5975,19 +5981,19 @@
         <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C60" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E60" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F60">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -5999,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>720</v>
+        <v>692</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -6017,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -6029,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>9531.360000000001</v>
+        <v>18300</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -6046,19 +6052,19 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C61" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D61" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F61">
-        <v>191</v>
+        <v>530</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6070,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>258</v>
+        <v>720</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -6088,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -6100,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="T61">
-        <v>3218.64</v>
+        <v>19062.72</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -6117,19 +6123,19 @@
         <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C62" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D62" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F62">
-        <v>336</v>
+        <v>191</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6141,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -6159,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -6171,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="T62">
-        <v>25156.8</v>
+        <v>4827.96</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -6188,19 +6194,19 @@
         <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C63" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D63" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>336</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6212,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>450</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -6230,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -6242,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>25156.8</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -6259,19 +6265,19 @@
         <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C64" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D64" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F64">
-        <v>302</v>
+        <v>6</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6283,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>425</v>
+        <v>6</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -6301,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -6313,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="T64">
-        <v>9889.83</v>
+        <v>0</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -6330,19 +6336,19 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C65" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D65" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F65">
-        <v>227</v>
+        <v>302</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6354,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>308</v>
+        <v>425</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -6372,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -6384,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>11898.3</v>
+        <v>6593.22</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -6401,19 +6407,19 @@
         <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C66" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D66" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F66">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6425,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -6443,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -6455,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="T66">
-        <v>4151.69</v>
+        <v>11898.3</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -6472,19 +6478,19 @@
         <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C67" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D67" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67">
-        <v>2097</v>
+        <v>154</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6496,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>2978</v>
+        <v>200</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -6514,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -6526,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="T67">
-        <v>44946.56</v>
+        <v>4151.69</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -6543,19 +6549,19 @@
         <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D68" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68">
-        <v>5928</v>
+        <v>2097</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6567,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>8454</v>
+        <v>2978</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -6585,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -6597,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="T68">
-        <v>245360.1</v>
+        <v>51991.43</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -6614,19 +6620,19 @@
         <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C69" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D69" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E69" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>5928</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6638,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>16</v>
+        <v>8454</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -6656,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -6668,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>324588.04</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -6685,16 +6691,19 @@
         <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C70" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D70" t="s">
-        <v>389</v>
+        <v>391</v>
+      </c>
+      <c r="E70" t="s">
+        <v>240</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -6706,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -6724,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="P70">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -6736,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="T70">
-        <v>19060.2</v>
+        <v>0</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -6753,19 +6762,16 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C71" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D71" t="s">
-        <v>390</v>
-      </c>
-      <c r="E71" t="s">
-        <v>245</v>
+        <v>392</v>
       </c>
       <c r="F71">
-        <v>4466</v>
+        <v>0</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -6777,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>6034</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -6795,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -6807,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="T71">
-        <v>32591.5</v>
+        <v>19060.2</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -6824,19 +6830,19 @@
         <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C72" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D72" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F72">
-        <v>3289</v>
+        <v>4466</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -6848,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>4888</v>
+        <v>6034</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -6866,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="P72">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -6878,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="T72">
-        <v>142424.66</v>
+        <v>39496.58</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -6895,19 +6901,19 @@
         <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C73" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D73" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F73">
-        <v>880</v>
+        <v>3289</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -6919,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>1107</v>
+        <v>4888</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -6937,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="P73">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -6949,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="T73">
-        <v>18503.4</v>
+        <v>168038.18</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -6966,19 +6972,19 @@
         <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>880</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -6990,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>61</v>
+        <v>1107</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -7008,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -7020,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>21587.3</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -7037,19 +7043,19 @@
         <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C75" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D75" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F75">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7061,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -7079,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -7091,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="T75">
-        <v>3770.34</v>
+        <v>0</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7108,19 +7114,19 @@
         <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C76" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D76" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F76">
-        <v>920</v>
+        <v>160</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7132,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <v>1089</v>
+        <v>204</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -7150,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="P76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -7162,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="T76">
-        <v>32201.7</v>
+        <v>3770.34</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -7179,19 +7185,19 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C77" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D77" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F77">
-        <v>242</v>
+        <v>920</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7203,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="J77">
-        <v>296</v>
+        <v>1089</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -7221,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -7233,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>32201.7</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -7250,19 +7256,19 @@
         <v>99</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C78" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D78" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78">
-        <v>52</v>
+        <v>242</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7274,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>57</v>
+        <v>296</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -7321,19 +7327,19 @@
         <v>100</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C79" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D79" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7345,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="J79">
-        <v>174</v>
+        <v>57</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -7363,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="P79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -7375,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="T79">
-        <v>10922.88</v>
+        <v>0</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -7392,19 +7398,19 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C80" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D80" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F80">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7416,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="J80">
-        <v>275</v>
+        <v>174</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -7434,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -7446,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="T80">
-        <v>8664.4</v>
+        <v>10922.88</v>
       </c>
       <c r="U80">
         <v>0</v>
@@ -7463,19 +7469,19 @@
         <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C81" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D81" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F81">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7487,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>542</v>
+        <v>275</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -7505,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -7517,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>8664.4</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7534,19 +7540,19 @@
         <v>103</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C82" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D82" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E82" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F82">
-        <v>14</v>
+        <v>444</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7558,7 +7564,7 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>16</v>
+        <v>542</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -7605,19 +7611,19 @@
         <v>104</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F83">
-        <v>3015</v>
+        <v>14</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -7629,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="J83">
-        <v>4787</v>
+        <v>16</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -7647,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -7659,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="T83">
-        <v>140338.77</v>
+        <v>0</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -7676,19 +7682,19 @@
         <v>105</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C84" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F84">
-        <v>17</v>
+        <v>3015</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -7700,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>20</v>
+        <v>4787</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -7718,7 +7724,7 @@
         <v>0</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -7730,7 +7736,7 @@
         <v>0</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>155109.93</v>
       </c>
       <c r="U84">
         <v>0</v>
@@ -7747,19 +7753,19 @@
         <v>106</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C85" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D85" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E85" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F85">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -7771,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -7789,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -7801,7 +7807,7 @@
         <v>0</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>7626.27</v>
       </c>
       <c r="U85">
         <v>0</v>
@@ -7818,19 +7824,19 @@
         <v>107</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C86" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D86" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F86">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -7842,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -7889,19 +7895,19 @@
         <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C87" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D87" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E87" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="F87">
-        <v>1347</v>
+        <v>6</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -7913,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>1759</v>
+        <v>9</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -7931,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -7943,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="T87">
-        <v>47440.68</v>
+        <v>0</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -7960,19 +7966,19 @@
         <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C88" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D88" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88">
-        <v>57</v>
+        <v>1347</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -7984,7 +7990,7 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>98</v>
+        <v>1759</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -8002,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -8014,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>47440.68</v>
       </c>
       <c r="U88">
         <v>0</v>
@@ -8031,19 +8037,19 @@
         <v>110</v>
       </c>
       <c r="B89" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="C89" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D89" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E89" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="F89">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8055,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -8073,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -8085,7 +8091,7 @@
         <v>0</v>
       </c>
       <c r="T89">
-        <v>1312.71</v>
+        <v>0</v>
       </c>
       <c r="U89">
         <v>0</v>
@@ -8102,19 +8108,19 @@
         <v>111</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C90" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D90" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E90" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F90">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8126,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -8144,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -8156,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="T90">
-        <v>-1863.56</v>
+        <v>1312.71</v>
       </c>
       <c r="U90">
         <v>0</v>
@@ -8173,19 +8179,19 @@
         <v>112</v>
       </c>
       <c r="B91" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="C91" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D91" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E91" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="F91">
-        <v>3606</v>
+        <v>50</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8197,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>4322</v>
+        <v>55</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -8215,7 +8221,7 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -8227,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="T91">
-        <v>45758.46</v>
+        <v>-1863.56</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -8244,19 +8250,19 @@
         <v>113</v>
       </c>
       <c r="B92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D92" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>3606</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8268,7 +8274,7 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>4322</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -8286,7 +8292,7 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -8298,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>45758.46</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -8315,19 +8321,19 @@
         <v>114</v>
       </c>
       <c r="B93" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C93" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D93" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E93" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F93">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8339,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -8386,19 +8392,19 @@
         <v>115</v>
       </c>
       <c r="B94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C94" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D94" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F94">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8410,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -8440,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="T94">
-        <v>1609.32</v>
+        <v>3551.07</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -8457,16 +8463,19 @@
         <v>116</v>
       </c>
       <c r="B95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C95" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D95" t="s">
-        <v>414</v>
+        <v>416</v>
+      </c>
+      <c r="E95" t="s">
+        <v>266</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -8478,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -8508,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="T95">
-        <v>2524.58</v>
+        <v>1609.32</v>
       </c>
       <c r="U95">
         <v>0</v>
@@ -8525,19 +8534,16 @@
         <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C96" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D96" t="s">
-        <v>415</v>
-      </c>
-      <c r="E96" t="s">
-        <v>266</v>
+        <v>417</v>
       </c>
       <c r="F96">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -8549,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -8567,7 +8573,7 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -8579,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="T96">
-        <v>11291.52</v>
+        <v>7573.74</v>
       </c>
       <c r="U96">
         <v>0</v>
@@ -8596,19 +8602,19 @@
         <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C97" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D97" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E97" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F97">
-        <v>317</v>
+        <v>244</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -8620,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <v>434</v>
+        <v>368</v>
       </c>
       <c r="K97">
         <v>0</v>
@@ -8638,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -8650,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="T97">
-        <v>9645.780000000001</v>
+        <v>12898.3</v>
       </c>
       <c r="U97">
         <v>0</v>
@@ -8667,19 +8673,19 @@
         <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C98" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D98" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F98">
-        <v>1011</v>
+        <v>317</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -8691,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>1512</v>
+        <v>434</v>
       </c>
       <c r="K98">
         <v>0</v>
@@ -8709,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -8721,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="T98">
-        <v>29720.25</v>
+        <v>9645.780000000001</v>
       </c>
       <c r="U98">
         <v>0</v>
@@ -8738,19 +8744,19 @@
         <v>120</v>
       </c>
       <c r="B99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C99" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D99" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F99">
-        <v>1507</v>
+        <v>1011</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -8762,7 +8768,7 @@
         <v>0</v>
       </c>
       <c r="J99">
-        <v>2233</v>
+        <v>1512</v>
       </c>
       <c r="K99">
         <v>0</v>
@@ -8780,7 +8786,7 @@
         <v>0</v>
       </c>
       <c r="P99">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -8792,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="T99">
-        <v>87818.36</v>
+        <v>36669.37</v>
       </c>
       <c r="U99">
         <v>0</v>
@@ -8809,19 +8815,19 @@
         <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C100" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D100" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F100">
-        <v>230</v>
+        <v>1507</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -8833,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="J100">
-        <v>287</v>
+        <v>2233</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -8851,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -8863,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="T100">
-        <v>4018.66</v>
+        <v>92492.92</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -8880,19 +8886,19 @@
         <v>122</v>
       </c>
       <c r="B101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C101" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D101" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F101">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -8904,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="J101">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -8922,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="P101">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -8934,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="T101">
-        <v>6475.42</v>
+        <v>4018.66</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -8951,19 +8957,19 @@
         <v>123</v>
       </c>
       <c r="B102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C102" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D102" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102">
-        <v>10172</v>
+        <v>171</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -8975,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="J102">
-        <v>13584</v>
+        <v>227</v>
       </c>
       <c r="K102">
         <v>0</v>
@@ -8993,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="P102">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -9005,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="T102">
-        <v>48035.57</v>
+        <v>6475.42</v>
       </c>
       <c r="U102">
         <v>0</v>
@@ -9022,16 +9028,19 @@
         <v>124</v>
       </c>
       <c r="B103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C103" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D103" t="s">
-        <v>422</v>
+        <v>424</v>
+      </c>
+      <c r="E103" t="s">
+        <v>274</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>10172</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -9043,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>13584</v>
       </c>
       <c r="K103">
         <v>0</v>
@@ -9061,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -9073,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>104077.08</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -9090,19 +9099,16 @@
         <v>125</v>
       </c>
       <c r="B104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C104" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D104" t="s">
-        <v>423</v>
-      </c>
-      <c r="E104" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="F104">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -9114,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="K104">
         <v>0</v>
@@ -9132,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -9144,7 +9150,7 @@
         <v>0</v>
       </c>
       <c r="T104">
-        <v>9828.82</v>
+        <v>0</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -9161,19 +9167,19 @@
         <v>126</v>
       </c>
       <c r="B105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C105" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D105" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F105">
-        <v>2351</v>
+        <v>607</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -9185,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="J105">
-        <v>3283</v>
+        <v>665</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -9203,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -9215,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="T105">
-        <v>14030.51</v>
+        <v>9828.82</v>
       </c>
       <c r="U105">
         <v>0</v>
@@ -9232,19 +9238,19 @@
         <v>127</v>
       </c>
       <c r="B106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C106" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D106" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F106">
-        <v>881</v>
+        <v>2351</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -9256,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="J106">
-        <v>1131</v>
+        <v>3283</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -9274,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -9286,7 +9292,7 @@
         <v>0</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>17538.13</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -9303,19 +9309,19 @@
         <v>128</v>
       </c>
       <c r="B107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C107" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D107" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F107">
-        <v>50</v>
+        <v>881</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -9327,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>64</v>
+        <v>1131</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -9345,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -9357,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="T107">
-        <v>1609.32</v>
+        <v>0</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -9374,19 +9380,19 @@
         <v>129</v>
       </c>
       <c r="B108" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C108" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D108" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E108" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F108">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -9398,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="K108">
         <v>0</v>
@@ -9416,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -9428,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>1609.32</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -9445,19 +9451,19 @@
         <v>130</v>
       </c>
       <c r="B109" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C109" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D109" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E109" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F109">
-        <v>2179</v>
+        <v>113</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -9469,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <v>3319</v>
+        <v>161</v>
       </c>
       <c r="K109">
         <v>0</v>
@@ -9487,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -9499,7 +9505,7 @@
         <v>0</v>
       </c>
       <c r="T109">
-        <v>85893.56</v>
+        <v>0</v>
       </c>
       <c r="U109">
         <v>0</v>
@@ -9516,19 +9522,19 @@
         <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C110" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D110" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F110">
-        <v>469</v>
+        <v>2179</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -9540,7 +9546,7 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <v>691</v>
+        <v>3319</v>
       </c>
       <c r="K110">
         <v>0</v>
@@ -9558,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -9570,7 +9576,7 @@
         <v>0</v>
       </c>
       <c r="T110">
-        <v>21344.09</v>
+        <v>101726.68</v>
       </c>
       <c r="U110">
         <v>0</v>
@@ -9587,19 +9593,19 @@
         <v>132</v>
       </c>
       <c r="B111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C111" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D111" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F111">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -9611,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <v>477</v>
+        <v>691</v>
       </c>
       <c r="K111">
         <v>0</v>
@@ -9629,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -9641,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="T111">
-        <v>19149.16</v>
+        <v>22868.67</v>
       </c>
       <c r="U111">
         <v>0</v>
@@ -9658,19 +9664,19 @@
         <v>133</v>
       </c>
       <c r="B112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C112" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D112" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F112">
-        <v>207</v>
+        <v>445</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -9682,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <v>274</v>
+        <v>477</v>
       </c>
       <c r="K112">
         <v>0</v>
@@ -9700,7 +9706,7 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -9712,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>19149.16</v>
       </c>
       <c r="U112">
         <v>0</v>
@@ -9729,19 +9735,19 @@
         <v>134</v>
       </c>
       <c r="B113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C113" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D113" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F113">
-        <v>585</v>
+        <v>207</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -9753,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>923</v>
+        <v>274</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -9771,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="P113">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -9783,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="T113">
-        <v>13973.74</v>
+        <v>0</v>
       </c>
       <c r="U113">
         <v>0</v>
@@ -9800,19 +9806,19 @@
         <v>135</v>
       </c>
       <c r="B114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C114" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D114" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F114">
-        <v>424</v>
+        <v>585</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -9824,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>651</v>
+        <v>923</v>
       </c>
       <c r="K114">
         <v>0</v>
@@ -9842,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="P114">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -9854,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="T114">
-        <v>15299.18</v>
+        <v>16514.42</v>
       </c>
       <c r="U114">
         <v>0</v>
@@ -9871,19 +9877,19 @@
         <v>136</v>
       </c>
       <c r="B115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C115" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D115" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F115">
-        <v>160</v>
+        <v>424</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -9895,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <v>218</v>
+        <v>651</v>
       </c>
       <c r="K115">
         <v>0</v>
@@ -9913,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -9925,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>20382.24</v>
       </c>
       <c r="U115">
         <v>0</v>
@@ -9942,19 +9948,19 @@
         <v>137</v>
       </c>
       <c r="B116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C116" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D116" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F116">
-        <v>7142</v>
+        <v>160</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -9966,7 +9972,7 @@
         <v>0</v>
       </c>
       <c r="J116">
-        <v>10180</v>
+        <v>218</v>
       </c>
       <c r="K116">
         <v>0</v>
@@ -9984,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -9996,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="T116">
-        <v>170185.92</v>
+        <v>0</v>
       </c>
       <c r="U116">
         <v>0</v>
@@ -10013,19 +10019,19 @@
         <v>138</v>
       </c>
       <c r="B117" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C117" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D117" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E117" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F117">
-        <v>3771</v>
+        <v>7142</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -10037,7 +10043,7 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <v>5733</v>
+        <v>10180</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -10055,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -10067,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="T117">
-        <v>83842.38</v>
+        <v>197002.88</v>
       </c>
       <c r="U117">
         <v>0</v>
@@ -10084,19 +10090,19 @@
         <v>139</v>
       </c>
       <c r="B118" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C118" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D118" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E118" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F118">
-        <v>1387</v>
+        <v>3771</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -10108,7 +10114,7 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>1775</v>
+        <v>5733</v>
       </c>
       <c r="K118">
         <v>0</v>
@@ -10126,7 +10132,7 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -10138,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="T118">
-        <v>16945.76</v>
+        <v>133922.04</v>
       </c>
       <c r="U118">
         <v>0</v>
@@ -10155,19 +10161,19 @@
         <v>140</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C119" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D119" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E119" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F119">
-        <v>6019</v>
+        <v>1387</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -10179,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="J119">
-        <v>8207</v>
+        <v>1775</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -10197,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -10209,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="T119">
-        <v>106631.32</v>
+        <v>16945.76</v>
       </c>
       <c r="U119">
         <v>0</v>
@@ -10226,19 +10232,19 @@
         <v>141</v>
       </c>
       <c r="B120" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C120" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D120" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E120" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F120">
-        <v>983</v>
+        <v>6019</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -10250,7 +10256,7 @@
         <v>0</v>
       </c>
       <c r="J120">
-        <v>1285</v>
+        <v>8207</v>
       </c>
       <c r="K120">
         <v>0</v>
@@ -10268,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="P120">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -10280,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="T120">
-        <v>6679.66</v>
+        <v>116748.26</v>
       </c>
       <c r="U120">
         <v>0</v>
@@ -10297,16 +10303,19 @@
         <v>142</v>
       </c>
       <c r="B121" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C121" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D121" t="s">
-        <v>440</v>
+        <v>442</v>
+      </c>
+      <c r="E121" t="s">
+        <v>291</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -10318,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="K121">
         <v>0</v>
@@ -10336,7 +10345,7 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -10348,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="T121">
-        <v>153573.76</v>
+        <v>6679.66</v>
       </c>
       <c r="U121">
         <v>0</v>
@@ -10365,19 +10374,16 @@
         <v>143</v>
       </c>
       <c r="B122" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="C122" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D122" t="s">
-        <v>441</v>
-      </c>
-      <c r="E122" t="s">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="F122">
-        <v>675</v>
+        <v>0</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -10389,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="J122">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="K122">
         <v>0</v>
@@ -10407,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -10419,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="T122">
-        <v>21607.63</v>
+        <v>160250.88</v>
       </c>
       <c r="U122">
         <v>0</v>
@@ -10436,19 +10442,19 @@
         <v>144</v>
       </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C123" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D123" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E123" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="F123">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -10460,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="J123">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="K123">
         <v>0</v>
@@ -10478,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="P123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -10490,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="T123">
-        <v>10166.11</v>
+        <v>21607.63</v>
       </c>
       <c r="U123">
         <v>0</v>
@@ -10507,19 +10513,19 @@
         <v>145</v>
       </c>
       <c r="B124" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C124" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D124" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E124" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="F124">
-        <v>150</v>
+        <v>688</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -10531,7 +10537,7 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <v>182</v>
+        <v>911</v>
       </c>
       <c r="K124">
         <v>0</v>
@@ -10561,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="T124">
-        <v>1861.02</v>
+        <v>10166.11</v>
       </c>
       <c r="U124">
         <v>0</v>
@@ -10578,19 +10584,19 @@
         <v>146</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C125" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D125" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F125">
-        <v>1456</v>
+        <v>150</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -10602,7 +10608,7 @@
         <v>0</v>
       </c>
       <c r="J125">
-        <v>1854</v>
+        <v>182</v>
       </c>
       <c r="K125">
         <v>0</v>
@@ -10620,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -10632,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="T125">
-        <v>21607.62</v>
+        <v>1861.02</v>
       </c>
       <c r="U125">
         <v>0</v>
@@ -10649,19 +10655,19 @@
         <v>147</v>
       </c>
       <c r="B126" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D126" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E126" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F126">
-        <v>960</v>
+        <v>1456</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -10673,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="J126">
-        <v>1272</v>
+        <v>1854</v>
       </c>
       <c r="K126">
         <v>0</v>
@@ -10691,7 +10697,7 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -10703,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="T126">
-        <v>20076.25</v>
+        <v>28810.16</v>
       </c>
       <c r="U126">
         <v>0</v>
@@ -10720,19 +10726,19 @@
         <v>148</v>
       </c>
       <c r="B127" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C127" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D127" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E127" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F127">
-        <v>622</v>
+        <v>960</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -10744,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="J127">
-        <v>827</v>
+        <v>1272</v>
       </c>
       <c r="K127">
         <v>0</v>
@@ -10774,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="T127">
-        <v>14826.25</v>
+        <v>20076.25</v>
       </c>
       <c r="U127">
         <v>0</v>
@@ -10791,19 +10797,19 @@
         <v>149</v>
       </c>
       <c r="B128" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C128" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D128" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E128" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F128">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -10815,7 +10821,7 @@
         <v>0</v>
       </c>
       <c r="J128">
-        <v>460</v>
+        <v>827</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -10833,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -10845,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="T128">
-        <v>8844.059999999999</v>
+        <v>17791.51</v>
       </c>
       <c r="U128">
         <v>0</v>
@@ -10862,19 +10868,19 @@
         <v>150</v>
       </c>
       <c r="B129" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C129" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D129" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E129" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F129">
-        <v>484</v>
+        <v>319</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -10886,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="J129">
-        <v>648</v>
+        <v>460</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -10904,7 +10910,7 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -10916,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="T129">
-        <v>8442.370000000001</v>
+        <v>8844.059999999999</v>
       </c>
       <c r="U129">
         <v>0</v>
@@ -10933,19 +10939,19 @@
         <v>151</v>
       </c>
       <c r="B130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C130" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D130" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F130">
-        <v>10726</v>
+        <v>484</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -10957,7 +10963,7 @@
         <v>0</v>
       </c>
       <c r="J130">
-        <v>14838</v>
+        <v>648</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -10975,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -10987,7 +10993,7 @@
         <v>0</v>
       </c>
       <c r="T130">
-        <v>314648.59</v>
+        <v>8442.370000000001</v>
       </c>
       <c r="U130">
         <v>0</v>
@@ -11004,19 +11010,19 @@
         <v>152</v>
       </c>
       <c r="B131" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C131" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D131" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E131" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F131">
-        <v>24</v>
+        <v>10726</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -11028,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="J131">
-        <v>26</v>
+        <v>14838</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -11046,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="P131">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -11058,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="T131">
-        <v>828.85</v>
+        <v>385824.91</v>
       </c>
       <c r="U131">
         <v>0</v>
@@ -11075,19 +11081,19 @@
         <v>153</v>
       </c>
       <c r="B132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C132" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D132" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F132">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -11099,7 +11105,7 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -11117,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -11129,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>828.85</v>
       </c>
       <c r="U132">
         <v>0</v>
@@ -11146,19 +11152,19 @@
         <v>154</v>
       </c>
       <c r="B133" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C133" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D133" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E133" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F133">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -11170,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -11188,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="P133">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -11200,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="T133">
-        <v>6475.43</v>
+        <v>0</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -11217,19 +11223,19 @@
         <v>155</v>
       </c>
       <c r="B134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F134">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -11241,7 +11247,7 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -11259,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -11271,7 +11277,7 @@
         <v>0</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>6475.43</v>
       </c>
       <c r="U134">
         <v>0</v>
@@ -11288,19 +11294,19 @@
         <v>156</v>
       </c>
       <c r="B135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C135" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D135" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F135">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -11312,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -11359,19 +11365,19 @@
         <v>157</v>
       </c>
       <c r="B136" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C136" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D136" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E136" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F136">
-        <v>248</v>
+        <v>30</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -11383,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>374</v>
+        <v>39</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -11401,7 +11407,7 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -11413,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="T136">
-        <v>5036.44</v>
+        <v>0</v>
       </c>
       <c r="U136">
         <v>0</v>
@@ -11430,19 +11436,19 @@
         <v>158</v>
       </c>
       <c r="B137" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C137" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D137" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E137" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F137">
-        <v>69</v>
+        <v>248</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -11454,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>85</v>
+        <v>374</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -11472,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -11484,7 +11490,7 @@
         <v>0</v>
       </c>
       <c r="T137">
-        <v>2540.68</v>
+        <v>5036.44</v>
       </c>
       <c r="U137">
         <v>0</v>
@@ -11501,19 +11507,19 @@
         <v>159</v>
       </c>
       <c r="B138" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C138" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D138" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E138" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F138">
-        <v>359</v>
+        <v>69</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -11525,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>464</v>
+        <v>85</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -11543,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -11555,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="T138">
-        <v>19065.24</v>
+        <v>2540.68</v>
       </c>
       <c r="U138">
         <v>0</v>
@@ -11572,19 +11578,19 @@
         <v>160</v>
       </c>
       <c r="B139" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C139" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D139" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E139" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F139">
-        <v>180</v>
+        <v>359</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -11596,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>209</v>
+        <v>464</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -11614,7 +11620,7 @@
         <v>0</v>
       </c>
       <c r="P139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -11626,7 +11632,7 @@
         <v>0</v>
       </c>
       <c r="T139">
-        <v>4236.44</v>
+        <v>25420.32</v>
       </c>
       <c r="U139">
         <v>0</v>
@@ -11643,19 +11649,19 @@
         <v>161</v>
       </c>
       <c r="B140" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C140" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D140" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E140" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F140">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -11667,7 +11673,7 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -11685,7 +11691,7 @@
         <v>0</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -11697,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>4236.44</v>
       </c>
       <c r="U140">
         <v>0</v>
@@ -11714,19 +11720,19 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C141" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D141" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E141" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F141">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -11738,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="K141">
         <v>0</v>
@@ -11785,19 +11791,19 @@
         <v>163</v>
       </c>
       <c r="B142" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C142" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D142" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E142" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F142">
-        <v>157</v>
+        <v>11</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -11809,7 +11815,7 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -11827,7 +11833,7 @@
         <v>0</v>
       </c>
       <c r="P142">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -11839,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="T142">
-        <v>7624.58</v>
+        <v>0</v>
       </c>
       <c r="U142">
         <v>0</v>
@@ -11856,19 +11862,19 @@
         <v>164</v>
       </c>
       <c r="B143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C143" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D143" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F143">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -11880,7 +11886,7 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -11898,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -11910,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="T143">
-        <v>2795.76</v>
+        <v>7624.58</v>
       </c>
       <c r="U143">
         <v>0</v>
@@ -11927,19 +11933,19 @@
         <v>165</v>
       </c>
       <c r="B144" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C144" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D144" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E144" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F144">
-        <v>2844</v>
+        <v>19</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -11951,7 +11957,7 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <v>4166</v>
+        <v>35</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -11969,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="P144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -11981,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="T144">
-        <v>85422.04000000001</v>
+        <v>2795.76</v>
       </c>
       <c r="U144">
         <v>0</v>
@@ -11998,19 +12004,19 @@
         <v>166</v>
       </c>
       <c r="B145" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C145" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D145" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E145" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F145">
-        <v>3609</v>
+        <v>2844</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -12022,7 +12028,7 @@
         <v>0</v>
       </c>
       <c r="J145">
-        <v>5078</v>
+        <v>4166</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -12040,7 +12046,7 @@
         <v>0</v>
       </c>
       <c r="P145">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -12052,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="T145">
-        <v>107395.8</v>
+        <v>85422.04000000001</v>
       </c>
       <c r="U145">
         <v>0</v>
@@ -12069,19 +12075,19 @@
         <v>167</v>
       </c>
       <c r="B146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C146" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D146" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F146">
-        <v>19</v>
+        <v>3609</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -12093,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <v>29</v>
+        <v>5078</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -12111,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -12123,7 +12129,7 @@
         <v>0</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>124300.05</v>
       </c>
       <c r="U146">
         <v>0</v>
@@ -12140,19 +12146,19 @@
         <v>168</v>
       </c>
       <c r="B147" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C147" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D147" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E147" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F147">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -12164,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -12182,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -12194,7 +12200,7 @@
         <v>0</v>
       </c>
       <c r="T147">
-        <v>24912.71</v>
+        <v>0</v>
       </c>
       <c r="U147">
         <v>0</v>
@@ -12211,19 +12217,19 @@
         <v>169</v>
       </c>
       <c r="B148" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C148" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D148" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E148" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -12235,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -12253,7 +12259,7 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -12265,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>24912.71</v>
       </c>
       <c r="U148">
         <v>0</v>
@@ -12282,19 +12288,19 @@
         <v>170</v>
       </c>
       <c r="B149" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C149" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D149" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E149" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F149">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -12306,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="J149">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -12353,19 +12359,19 @@
         <v>171</v>
       </c>
       <c r="B150" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="C150" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D150" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E150" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="F150">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -12377,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -12424,19 +12430,19 @@
         <v>172</v>
       </c>
       <c r="B151" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C151" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D151" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E151" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F151">
-        <v>256</v>
+        <v>123</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -12448,7 +12454,7 @@
         <v>0</v>
       </c>
       <c r="J151">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -12466,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -12478,7 +12484,7 @@
         <v>0</v>
       </c>
       <c r="T151">
-        <v>5931.36</v>
+        <v>0</v>
       </c>
       <c r="U151">
         <v>0</v>
@@ -12495,19 +12501,19 @@
         <v>173</v>
       </c>
       <c r="B152" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="C152" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D152" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E152" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="F152">
-        <v>628</v>
+        <v>256</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -12519,7 +12525,7 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <v>666</v>
+        <v>301</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -12549,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="T152">
-        <v>8897.459999999999</v>
+        <v>5931.36</v>
       </c>
       <c r="U152">
         <v>0</v>
@@ -12566,19 +12572,19 @@
         <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C153" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D153" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F153">
-        <v>990</v>
+        <v>628</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -12590,7 +12596,7 @@
         <v>0</v>
       </c>
       <c r="J153">
-        <v>1150</v>
+        <v>666</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -12608,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -12620,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="T153">
-        <v>29659.32</v>
+        <v>8897.459999999999</v>
       </c>
       <c r="U153">
         <v>0</v>
@@ -12637,19 +12643,19 @@
         <v>175</v>
       </c>
       <c r="B154" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C154" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D154" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F154">
-        <v>697</v>
+        <v>990</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -12661,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <v>860</v>
+        <v>1150</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -12679,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -12691,7 +12697,7 @@
         <v>0</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>29659.32</v>
       </c>
       <c r="U154">
         <v>0</v>
@@ -12708,69 +12714,140 @@
         <v>176</v>
       </c>
       <c r="B155" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C155" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D155" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E155" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F155">
+        <v>697</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>860</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <v>0</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155">
+        <v>0</v>
+      </c>
+      <c r="V155">
+        <v>0</v>
+      </c>
+      <c r="W155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23">
+      <c r="A156" t="s">
+        <v>177</v>
+      </c>
+      <c r="B156" t="s">
+        <v>322</v>
+      </c>
+      <c r="C156" t="s">
+        <v>477</v>
+      </c>
+      <c r="D156" t="s">
+        <v>477</v>
+      </c>
+      <c r="E156" t="s">
+        <v>322</v>
+      </c>
+      <c r="F156">
         <v>360</v>
       </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-      <c r="J155">
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
         <v>437</v>
       </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <v>0</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
         <v>5</v>
       </c>
-      <c r="Q155">
-        <v>0</v>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155">
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156">
         <v>9809.32</v>
       </c>
-      <c r="U155">
-        <v>0</v>
-      </c>
-      <c r="V155">
-        <v>0</v>
-      </c>
-      <c r="W155">
+      <c r="U156">
+        <v>0</v>
+      </c>
+      <c r="V156">
+        <v>0</v>
+      </c>
+      <c r="W156">
         <v>0</v>
       </c>
     </row>
